--- a/artfynd/A 56000-2024 artfynd.xlsx
+++ b/artfynd/A 56000-2024 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121589327</v>
+        <v>121589330</v>
       </c>
       <c r="B3" t="n">
-        <v>78609</v>
+        <v>56568</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -819,16 +819,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Fäboliden, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>647518</v>
+        <v>647460</v>
       </c>
       <c r="R3" t="n">
-        <v>7166825</v>
+        <v>7166768</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -865,7 +870,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På klen senvuxen gran</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121589325</v>
+        <v>121589328</v>
       </c>
       <c r="B4" t="n">
-        <v>91006</v>
+        <v>91996</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,30 +909,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -936,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>647542</v>
+        <v>647463</v>
       </c>
       <c r="R4" t="n">
-        <v>7166824</v>
+        <v>7166772</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -972,11 +977,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-08-13</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1109,10 +1109,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121589330</v>
+        <v>121589325</v>
       </c>
       <c r="B6" t="n">
-        <v>56568</v>
+        <v>91006</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1121,25 +1121,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1147,21 +1147,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Fäboliden, Ly lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>647460</v>
+        <v>647542</v>
       </c>
       <c r="R6" t="n">
-        <v>7166768</v>
+        <v>7166824</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1198,7 +1193,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1225,10 +1220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121589328</v>
+        <v>121589327</v>
       </c>
       <c r="B7" t="n">
-        <v>91996</v>
+        <v>78609</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1237,30 +1232,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1269,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>647463</v>
+        <v>647518</v>
       </c>
       <c r="R7" t="n">
-        <v>7166772</v>
+        <v>7166825</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1305,6 +1300,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På klen senvuxen gran</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 56000-2024 artfynd.xlsx
+++ b/artfynd/A 56000-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121589329</v>
+        <v>121589325</v>
       </c>
       <c r="B2" t="n">
-        <v>91996</v>
+        <v>91006</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>647453</v>
+        <v>647542</v>
       </c>
       <c r="R2" t="n">
-        <v>7166763</v>
+        <v>7166824</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -755,6 +755,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121589330</v>
+        <v>121589328</v>
       </c>
       <c r="B3" t="n">
-        <v>56568</v>
+        <v>91996</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,31 +802,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>647460</v>
+        <v>647463</v>
       </c>
       <c r="R3" t="n">
-        <v>7166768</v>
+        <v>7166772</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -866,11 +866,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-08-13</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121589328</v>
+        <v>121589330</v>
       </c>
       <c r="B4" t="n">
-        <v>91996</v>
+        <v>56568</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,26 +908,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>647463</v>
+        <v>647460</v>
       </c>
       <c r="R4" t="n">
-        <v>7166772</v>
+        <v>7166768</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -977,6 +977,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1109,10 +1114,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121589325</v>
+        <v>121589329</v>
       </c>
       <c r="B6" t="n">
-        <v>91006</v>
+        <v>91996</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1121,30 +1126,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1153,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>647542</v>
+        <v>647453</v>
       </c>
       <c r="R6" t="n">
-        <v>7166824</v>
+        <v>7166763</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1189,11 +1194,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-08-13</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 56000-2024 artfynd.xlsx
+++ b/artfynd/A 56000-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121589325</v>
+        <v>121589329</v>
       </c>
       <c r="B2" t="n">
-        <v>91006</v>
+        <v>92004</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>647542</v>
+        <v>647453</v>
       </c>
       <c r="R2" t="n">
-        <v>7166824</v>
+        <v>7166763</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -755,11 +755,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-08-13</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121589328</v>
+        <v>121589330</v>
       </c>
       <c r="B3" t="n">
-        <v>91996</v>
+        <v>56569</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,26 +797,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>647463</v>
+        <v>647460</v>
       </c>
       <c r="R3" t="n">
-        <v>7166772</v>
+        <v>7166768</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -866,6 +866,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121589330</v>
+        <v>121589328</v>
       </c>
       <c r="B4" t="n">
-        <v>56568</v>
+        <v>92004</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,31 +913,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>647460</v>
+        <v>647463</v>
       </c>
       <c r="R4" t="n">
-        <v>7166768</v>
+        <v>7166772</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -977,11 +977,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-08-13</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,7 +1006,7 @@
         <v>121589326</v>
       </c>
       <c r="B5" t="n">
-        <v>79718</v>
+        <v>79725</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1114,10 +1109,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121589329</v>
+        <v>121589325</v>
       </c>
       <c r="B6" t="n">
-        <v>91996</v>
+        <v>91014</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1126,30 +1121,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1158,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>647453</v>
+        <v>647542</v>
       </c>
       <c r="R6" t="n">
-        <v>7166763</v>
+        <v>7166824</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1194,6 +1189,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,7 +1223,7 @@
         <v>121589327</v>
       </c>
       <c r="B7" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 56000-2024 artfynd.xlsx
+++ b/artfynd/A 56000-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121589326</v>
+        <v>121589330</v>
       </c>
       <c r="B2" t="n">
-        <v>79725</v>
+        <v>56569</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6461</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,16 +713,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Fäboliden, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>647520</v>
+        <v>647460</v>
       </c>
       <c r="R2" t="n">
-        <v>7166823</v>
+        <v>7166768</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -755,6 +760,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121589327</v>
+        <v>121589329</v>
       </c>
       <c r="B3" t="n">
-        <v>78616</v>
+        <v>92004</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,30 +803,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -825,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>647518</v>
+        <v>647453</v>
       </c>
       <c r="R3" t="n">
-        <v>7166825</v>
+        <v>7166763</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -861,11 +871,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-08-13</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På klen senvuxen gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121589330</v>
+        <v>121589325</v>
       </c>
       <c r="B4" t="n">
-        <v>56569</v>
+        <v>91014</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -930,21 +935,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Fäboliden, Ly lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>647460</v>
+        <v>647542</v>
       </c>
       <c r="R4" t="n">
-        <v>7166768</v>
+        <v>7166824</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -981,7 +981,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121589328</v>
+        <v>121589327</v>
       </c>
       <c r="B5" t="n">
-        <v>92004</v>
+        <v>78616</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,30 +1020,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>647463</v>
+        <v>647518</v>
       </c>
       <c r="R5" t="n">
-        <v>7166772</v>
+        <v>7166825</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1088,6 +1088,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På klen senvuxen gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1114,7 +1119,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121589329</v>
+        <v>121589328</v>
       </c>
       <c r="B6" t="n">
         <v>92004</v>
@@ -1149,7 +1154,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1158,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>647453</v>
+        <v>647463</v>
       </c>
       <c r="R6" t="n">
-        <v>7166763</v>
+        <v>7166772</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1220,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121589325</v>
+        <v>121589326</v>
       </c>
       <c r="B7" t="n">
-        <v>91014</v>
+        <v>79725</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1232,25 +1237,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>6461</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1264,10 +1269,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>647542</v>
+        <v>647520</v>
       </c>
       <c r="R7" t="n">
-        <v>7166824</v>
+        <v>7166823</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1300,11 +1305,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-08-13</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 56000-2024 artfynd.xlsx
+++ b/artfynd/A 56000-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121589330</v>
+        <v>121589326</v>
       </c>
       <c r="B2" t="n">
-        <v>56569</v>
+        <v>79725</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>6461</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,21 +713,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Fäboliden, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>647460</v>
+        <v>647520</v>
       </c>
       <c r="R2" t="n">
-        <v>7166768</v>
+        <v>7166823</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -760,11 +755,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-08-13</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -897,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121589325</v>
+        <v>121589327</v>
       </c>
       <c r="B4" t="n">
-        <v>91014</v>
+        <v>78616</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>647542</v>
+        <v>647518</v>
       </c>
       <c r="R4" t="n">
-        <v>7166824</v>
+        <v>7166825</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -981,7 +971,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På klen senvuxen gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121589327</v>
+        <v>121589330</v>
       </c>
       <c r="B5" t="n">
-        <v>78616</v>
+        <v>56569</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,25 +1010,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1046,16 +1036,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Fäboliden, Ly lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>647518</v>
+        <v>647460</v>
       </c>
       <c r="R5" t="n">
-        <v>7166825</v>
+        <v>7166768</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1092,7 +1087,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På klen senvuxen gran</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1225,10 +1220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121589326</v>
+        <v>121589325</v>
       </c>
       <c r="B7" t="n">
-        <v>79725</v>
+        <v>91014</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1237,25 +1232,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6461</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1269,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>647520</v>
+        <v>647542</v>
       </c>
       <c r="R7" t="n">
-        <v>7166823</v>
+        <v>7166824</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1305,6 +1300,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 56000-2024 artfynd.xlsx
+++ b/artfynd/A 56000-2024 artfynd.xlsx
@@ -675,42 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121589329</v>
+        <v>121589325</v>
       </c>
       <c r="B2" t="n">
-        <v>92018</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>647453</v>
+        <v>647542</v>
       </c>
       <c r="R2" t="n">
-        <v>7166763</v>
+        <v>7166824</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -755,6 +750,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121589327</v>
+        <v>121589328</v>
       </c>
       <c r="B3" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,26 +792,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -825,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>647518</v>
+        <v>647463</v>
       </c>
       <c r="R3" t="n">
-        <v>7166825</v>
+        <v>7166772</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -861,11 +856,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-08-13</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På klen senvuxen gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,42 +882,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121589326</v>
+        <v>121589329</v>
       </c>
       <c r="B4" t="n">
-        <v>79738</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6461</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -936,10 +921,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>647520</v>
+        <v>647453</v>
       </c>
       <c r="R4" t="n">
-        <v>7166823</v>
+        <v>7166763</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -998,42 +983,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121589328</v>
+        <v>121589327</v>
       </c>
       <c r="B5" t="n">
-        <v>92018</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1042,10 +1022,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>647463</v>
+        <v>647518</v>
       </c>
       <c r="R5" t="n">
-        <v>7166772</v>
+        <v>7166825</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1078,6 +1058,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På klen senvuxen gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1104,37 +1089,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121589325</v>
+        <v>121589326</v>
       </c>
       <c r="B6" t="n">
-        <v>91028</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80460</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>6461</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1148,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>647542</v>
+        <v>647520</v>
       </c>
       <c r="R6" t="n">
-        <v>7166824</v>
+        <v>7166823</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1184,11 +1164,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-08-13</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1218,12 +1193,7 @@
         <v>121589330</v>
       </c>
       <c r="B7" t="n">
-        <v>56577</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 56000-2024 artfynd.xlsx
+++ b/artfynd/A 56000-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589325</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589328</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -980,6 +995,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589329</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1086,6 +1106,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589327</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1187,6 +1212,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589326</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1298,8 +1328,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589330</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>